--- a/docs/Diagrama de Gantt dia a dia.xlsx
+++ b/docs/Diagrama de Gantt dia a dia.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{747172FA-9831-4B44-B565-0C150BF134E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9459EA1B-9342-4DB1-9845-01D5546C8745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2018,35 +2018,7 @@
     <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" customWidth="1"/>
     <col min="8" max="8" width="9.44140625" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="3.33203125" customWidth="1"/>
-    <col min="15" max="15" width="9.6640625" customWidth="1"/>
-    <col min="16" max="49" width="3.33203125" customWidth="1"/>
-    <col min="50" max="50" width="7.109375" customWidth="1"/>
-    <col min="51" max="56" width="3.33203125" customWidth="1"/>
-    <col min="57" max="57" width="7" customWidth="1"/>
-    <col min="58" max="63" width="3.33203125" customWidth="1"/>
-    <col min="64" max="64" width="6.109375" customWidth="1"/>
-    <col min="65" max="65" width="2.77734375" customWidth="1"/>
-    <col min="66" max="66" width="3.5546875" customWidth="1"/>
-    <col min="67" max="67" width="2.44140625" customWidth="1"/>
-    <col min="68" max="68" width="4.33203125" customWidth="1"/>
-    <col min="69" max="69" width="3.5546875" customWidth="1"/>
-    <col min="70" max="70" width="2.88671875" customWidth="1"/>
-    <col min="71" max="71" width="8.109375" customWidth="1"/>
-    <col min="72" max="72" width="2.77734375" customWidth="1"/>
-    <col min="73" max="73" width="3.5546875" customWidth="1"/>
-    <col min="74" max="74" width="2.44140625" customWidth="1"/>
-    <col min="75" max="75" width="4.33203125" customWidth="1"/>
-    <col min="76" max="76" width="3.5546875" customWidth="1"/>
-    <col min="77" max="77" width="2.88671875" customWidth="1"/>
-    <col min="78" max="78" width="8.6640625" customWidth="1"/>
-    <col min="79" max="79" width="2.77734375" customWidth="1"/>
-    <col min="80" max="80" width="3.5546875" customWidth="1"/>
-    <col min="81" max="81" width="2.44140625" customWidth="1"/>
-    <col min="82" max="82" width="4.33203125" customWidth="1"/>
-    <col min="83" max="83" width="3.5546875" customWidth="1"/>
-    <col min="84" max="84" width="2.88671875" customWidth="1"/>
-    <col min="85" max="85" width="5.33203125" customWidth="1"/>
+    <col min="9" max="85" width="3.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3062,18 +3034,18 @@
         <v>43</v>
       </c>
       <c r="D9" s="17">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="75">
         <v>46293</v>
       </c>
       <c r="F9" s="75">
-        <v>46299</v>
+        <v>46295</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
@@ -3458,13 +3430,13 @@
         <v>43</v>
       </c>
       <c r="D13" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="75">
-        <v>46311</v>
+        <v>46293</v>
       </c>
       <c r="F13" s="75">
-        <v>46313</v>
+        <v>46295</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
